--- a/artfynd/A 33359-2024 artfynd.xlsx
+++ b/artfynd/A 33359-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126092963</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126093041</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126092978</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33359-2024 artfynd.xlsx
+++ b/artfynd/A 33359-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126092963</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126093041</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126092978</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33359-2024 artfynd.xlsx
+++ b/artfynd/A 33359-2024 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126093041</v>
+        <v>126092978</v>
       </c>
       <c r="B3" t="n">
         <v>78977</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507027</v>
+        <v>507079</v>
       </c>
       <c r="R3" t="n">
-        <v>6846419</v>
+        <v>6846407</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126092978</v>
+        <v>126093041</v>
       </c>
       <c r="B4" t="n">
         <v>78977</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507079</v>
+        <v>507027</v>
       </c>
       <c r="R4" t="n">
-        <v>6846407</v>
+        <v>6846419</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 33359-2024 artfynd.xlsx
+++ b/artfynd/A 33359-2024 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126092978</v>
+        <v>126093041</v>
       </c>
       <c r="B3" t="n">
         <v>78977</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507079</v>
+        <v>507027</v>
       </c>
       <c r="R3" t="n">
-        <v>6846407</v>
+        <v>6846419</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126093041</v>
+        <v>126092978</v>
       </c>
       <c r="B4" t="n">
         <v>78977</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507027</v>
+        <v>507079</v>
       </c>
       <c r="R4" t="n">
-        <v>6846419</v>
+        <v>6846407</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 33359-2024 artfynd.xlsx
+++ b/artfynd/A 33359-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126092963</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126093041</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126092978</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
